--- a/data.mn/public/datasets/hospital-bed-density.xlsx
+++ b/data.mn/public/datasets/hospital-bed-density.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,270 +414,628 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="8" customWidth="1" min="23" max="23"/>
-    <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="8" customWidth="1" min="25" max="25"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="8" customWidth="1" min="30" max="30"/>
-    <col width="8" customWidth="1" min="31" max="31"/>
-    <col width="8" customWidth="1" min="32" max="32"/>
-    <col width="8" customWidth="1" min="33" max="33"/>
-    <col width="8" customWidth="1" min="34" max="34"/>
-    <col width="8" customWidth="1" min="35" max="35"/>
-    <col width="8" customWidth="1" min="36" max="36"/>
-    <col width="8" customWidth="1" min="37" max="37"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" t="n">
-        <v>1989</v>
-      </c>
-      <c r="C1" t="n">
-        <v>1990</v>
-      </c>
-      <c r="D1" t="n">
-        <v>1991</v>
-      </c>
-      <c r="E1" t="n">
-        <v>1992</v>
-      </c>
-      <c r="F1" t="n">
-        <v>1993</v>
-      </c>
-      <c r="G1" t="n">
-        <v>1994</v>
-      </c>
-      <c r="H1" t="n">
-        <v>1995</v>
-      </c>
-      <c r="I1" t="n">
-        <v>1996</v>
-      </c>
-      <c r="J1" t="n">
-        <v>1997</v>
-      </c>
-      <c r="K1" t="n">
-        <v>1998</v>
-      </c>
-      <c r="L1" t="n">
-        <v>1999</v>
-      </c>
-      <c r="M1" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N1" t="n">
-        <v>2001</v>
-      </c>
-      <c r="O1" t="n">
-        <v>2002</v>
-      </c>
-      <c r="P1" t="n">
-        <v>2003</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>2004</v>
-      </c>
-      <c r="R1" t="n">
-        <v>2005</v>
-      </c>
-      <c r="S1" t="n">
-        <v>2006</v>
-      </c>
-      <c r="T1" t="n">
-        <v>2007</v>
-      </c>
-      <c r="U1" t="n">
-        <v>2008</v>
-      </c>
-      <c r="V1" t="n">
-        <v>2009</v>
-      </c>
-      <c r="W1" t="n">
-        <v>2010</v>
-      </c>
-      <c r="X1" t="n">
-        <v>2011</v>
-      </c>
-      <c r="Y1" t="n">
-        <v>2012</v>
-      </c>
-      <c r="Z1" t="n">
-        <v>2013</v>
-      </c>
-      <c r="AA1" t="n">
-        <v>2014</v>
-      </c>
-      <c r="AB1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="AC1" t="n">
-        <v>2016</v>
-      </c>
-      <c r="AD1" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AE1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AF1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AG1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="AH1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="AI1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="AJ1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="AK1" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>beds_per_1000</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1989</v>
+      </c>
       <c r="B2" t="n">
         <v>12</v>
       </c>
-      <c r="C2" t="n">
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B3" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B4" t="n">
         <v>12</v>
       </c>
-      <c r="E2" t="n">
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B5" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B6" t="n">
         <v>10</v>
       </c>
-      <c r="G2" t="n">
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B7" t="n">
         <v>10</v>
       </c>
-      <c r="H2" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B8" t="n">
         <v>10</v>
       </c>
-      <c r="I2" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B9" t="n">
         <v>10</v>
       </c>
-      <c r="J2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N2" t="n">
-        <v>8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>7</v>
-      </c>
-      <c r="R2" t="n">
-        <v>7</v>
-      </c>
-      <c r="S2" t="n">
-        <v>7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>7</v>
-      </c>
-      <c r="U2" t="n">
-        <v>7</v>
-      </c>
-      <c r="V2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W2" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B23" t="n">
         <v>6</v>
       </c>
-      <c r="X2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH2" t="n">
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B24" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B29" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B34" t="n">
         <v>11</v>
       </c>
-      <c r="AI2" t="n">
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B35" t="n">
         <v>9</v>
       </c>
-      <c r="AJ2" t="n">
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B36" t="n">
         <v>9</v>
       </c>
-      <c r="AK2" t="n">
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B37" t="n">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>мянган_хүн_тутамд_ор</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B24" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B29" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B34" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B35" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B36" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B37" t="n">
         <v>9</v>
       </c>
     </row>
